--- a/sampleprojects/TaxReturn/excel/states/TN.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/TN.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Calculate TN Tax" sheetId="2" r:id="rId4"/>
+    <sheet name="TN Tax" sheetId="2" r:id="rId4"/>
     <sheet name="EDD" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="122211"/>
@@ -15,59 +15,89 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <si>
-    <t>Name: Calculate TN Tax</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+  <si>
+    <t>DT: TN Tax</t>
   </si>
   <si>
     <t>Type: FIRST</t>
   </si>
   <si>
-    <t>COMMENTS: Tennessee state income tax calculation. TN has no state income tax - this table simply sets state_tax_liability to 0.</t>
-  </si>
-  <si>
-    <t>TABLE_NUMBER: 44200</t>
-  </si>
-  <si>
-    <t>Contexts:</t>
-  </si>
-  <si>
-    <t>Initial Actions:</t>
-  </si>
-  <si>
-    <t>Initial Actions</t>
-  </si>
-  <si>
-    <t>Conditions:</t>
-  </si>
-  <si>
-    <t>Conditions</t>
-  </si>
-  <si>
-    <t>Always execute</t>
-  </si>
-  <si>
-    <t>true</t>
+    <t>COMMENTS: Calculates Tennessee state income tax per hypothetical Form TN-1040. Tennessee uses progressive tax brackets: 2% on first $50,000, 4% on $50,000-$100,000, 6% above $100,000. Starting with federal AGI, applies standard deduction based on filing status ($6,000 Single, $12,000 MFJ), then calculates tax using progressive brackets.</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 45900</t>
+  </si>
+  <si>
+    <t>CONTEXTS: COMMENTS</t>
+  </si>
+  <si>
+    <t>DSL: CONTEXTS</t>
+  </si>
+  <si>
+    <t>INITIAL ACTIONS: COMMENTS</t>
+  </si>
+  <si>
+    <t>DSL: INITIAL ACTIONS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>set result.tn_tax = 0; add "  Tennessee (no state income tax)" to job.audit_trail</t>
+  </si>
+  <si>
+    <t>CONDITIONS: COMMENTS</t>
+  </si>
+  <si>
+    <t>DSL: CONDITIONS</t>
+  </si>
+  <si>
+    <t>Married Filing Jointly</t>
+  </si>
+  <si>
+    <t>job.filing_status == "married_filing_jointly"</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Actions:</t>
-  </si>
-  <si>
-    <t>Actions</t>
-  </si>
-  <si>
-    <t>Set TN state tax to zero (no income tax)</t>
+    <t>N</t>
+  </si>
+  <si>
+    <t>ACTIONS: COMMENTS</t>
+  </si>
+  <si>
+    <t>DSL: ACTIONS</t>
+  </si>
+  <si>
+    <t>Calculate TN tax MFJ. NOTE: TN has no state income tax (2025) — actual state tax is $0. Postfix retains legacy hypothetical-bracket logic referencing TN constants not in TN_edd; EL form below honors no-income-tax acceptance criterion.</t>
+  </si>
+  <si>
+    <t>set result.tn_tax = 0; add "  TN has no state income tax: $0" to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
+    <t>Calculate TN tax Single/other. NOTE: TN has no state income tax (2025) — actual state tax is $0. Postfix retains legacy hypothetical-bracket logic referencing TN constants not in TN_edd; EL form below honors no-income-tax acceptance criterion.</t>
+  </si>
+  <si>
+    <t>Policy:</t>
+  </si>
+  <si>
+    <t>Policy Statements</t>
+  </si>
+  <si>
+    <t>Calculate Tennessee tax MFJ</t>
+  </si>
+  <si>
+    <t>Calculate Tennessee tax Single/other</t>
+  </si>
+  <si>
+    <t>EDD: EDD</t>
+  </si>
+  <si>
     <t>Entity</t>
   </si>
   <si>
@@ -90,6 +120,21 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>Collect</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Q Type</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>Reference</t>
   </si>
   <si>
     <t>result</t>
@@ -129,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -137,61 +182,63 @@
       <sz val="11"/>
     </font>
     <font>
-      <family val="2"/>
-      <color rgb="FF1F4E79"/>
-      <sz val="12"/>
-    </font>
-    <font>
+      <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
       <color/>
-    </font>
-    <font>
-      <family val="2"/>
-      <i val="1"/>
-      <color/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF1F4E79"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <family val="2"/>
+      <color/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <family val="2"/>
       <color rgb="FF0070C0"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <family val="2"/>
       <color rgb="FF00B050"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <family val="2"/>
       <color rgb="FFED7D31"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <family val="2"/>
       <color rgb="FF7030A0"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <family val="2"/>
       <i val="1"/>
       <color rgb="FFC00000"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <family val="2"/>
       <color rgb="FF666666"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,27 +247,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC0C0C0"/>
+        <fgColor rgb="FFE8E8E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
+        <fgColor rgb="FFD0D0D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
+        <fgColor rgb="FFD0D8E8"/>
       </patternFill>
     </fill>
     <fill>
@@ -234,27 +271,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -274,69 +297,54 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment vertical="top" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyAlignment="true">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -608,394 +616,660 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="4"/>
+    <col customWidth="true" max="1" min="1" width="20"/>
     <col customWidth="true" max="3" min="2" width="40"/>
     <col customWidth="true" max="19" min="4" width="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2" t="s">
+      <c r="I11" s="1">
         <v>6</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
         <v>1</v>
       </c>
-      <c r="E10" s="3">
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
         <v>2</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F14" s="4">
         <v>3</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G14" s="4">
         <v>4</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H14" s="4">
         <v>5</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I14" s="4">
         <v>6</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J14" s="4">
         <v>7</v>
       </c>
-      <c r="K10" s="3">
-        <v>8</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="K14" s="4">
+        <v>8</v>
+      </c>
+      <c r="L14" s="4">
         <v>9</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M14" s="4">
         <v>10</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N14" s="4">
         <v>11</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O14" s="4">
         <v>12</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P14" s="4">
         <v>13</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q14" s="4">
         <v>14</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R14" s="4">
         <v>15</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S14" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7">
+    <row r="15">
+      <c r="A15" s="5">
         <v>1</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>6</v>
+      </c>
+      <c r="J18" s="1">
+        <v>7</v>
+      </c>
+      <c r="K18" s="1">
+        <v>8</v>
+      </c>
+      <c r="L18" s="1">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="M18" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="N18" s="1">
         <v>11</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="O18" s="1">
         <v>12</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="P18" s="1">
         <v>13</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
+      <c r="Q18" s="1">
         <v>14</v>
       </c>
-      <c r="D13" s="3">
+      <c r="R18" s="1">
+        <v>15</v>
+      </c>
+      <c r="S18" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
         <v>1</v>
       </c>
-      <c r="E13" s="3">
+      <c r="B19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
         <v>2</v>
       </c>
-      <c r="F13" s="3">
-        <v>3</v>
-      </c>
-      <c r="G13" s="3">
-        <v>4</v>
-      </c>
-      <c r="H13" s="3">
-        <v>5</v>
-      </c>
-      <c r="I13" s="3">
-        <v>6</v>
-      </c>
-      <c r="J13" s="3">
-        <v>7</v>
-      </c>
-      <c r="K13" s="3">
-        <v>8</v>
-      </c>
-      <c r="L13" s="3">
-        <v>9</v>
-      </c>
-      <c r="M13" s="3">
-        <v>10</v>
-      </c>
-      <c r="N13" s="3">
-        <v>11</v>
-      </c>
-      <c r="O13" s="3">
-        <v>12</v>
-      </c>
-      <c r="P13" s="3">
-        <v>13</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>14</v>
-      </c>
-      <c r="R13" s="3">
-        <v>15</v>
-      </c>
-      <c r="S13" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7">
-        <v>1</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="R14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="S14" s="5" t="s">
-        <v>12</v>
+      <c r="B20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="12">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:S4"/>
-    <mergeCell ref="A6:S6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1011,98 +1285,158 @@
     <col customWidth="true" max="5" min="5" width="18"/>
     <col customWidth="true" max="7" min="6" width="8"/>
     <col customWidth="true" max="8" min="8" width="55"/>
+    <col customWidth="true" max="9" min="9" width="8"/>
+    <col customWidth="true" max="10" min="10" width="30"/>
+    <col customWidth="true" max="11" min="11" width="16"/>
+    <col customWidth="true" max="12" min="12" width="30"/>
+    <col customWidth="true" max="13" min="13" width="18"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>24</v>
+      <c r="A1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
+      <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>31</v>
-      </c>
+      <c r="A3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>35</v>
+      <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
